--- a/02_PhanHoaiBao_Module02.xlsx
+++ b/02_PhanHoaiBao_Module02.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9000" firstSheet="7" activeTab="10"/>
+    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1" sheetId="1" r:id="rId1"/>
@@ -2653,8 +2653,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>179884</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>184162</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>8902</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2672,7 +2672,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10970260" y="270510"/>
-          <a:ext cx="5829935" cy="3964940"/>
+          <a:ext cx="5829935" cy="3614420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5534,7 +5534,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" ht="27.6" spans="1:8">
+    <row r="16" spans="1:8">
       <c r="A16" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5559,7 +5559,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" ht="27.6" spans="1:8">
+    <row r="17" spans="1:8">
       <c r="A17" s="34">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5584,7 +5584,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="18" ht="27.6" spans="1:8">
+    <row r="18" spans="1:8">
       <c r="A18" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5728,7 +5728,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" ht="27.6" spans="1:8">
+    <row r="24" spans="1:8">
       <c r="A24" s="34">
         <f t="shared" si="0"/>
         <v>13</v>
